--- a/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
+++ b/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,27 +518,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.5192003</t>
+          <t>-11.58001621</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-75.8991414</t>
+          <t>-75.95862675</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POLICLINICO SANTO REMEDIO</t>
+          <t>HUAYNACANCHA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JUNIN NUMERO 147 DISTRITO LA OROYA PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
+          <t>AVENIDA AV. 16 DE JUNIO S/N NUMERO S/N DISTRITO LA OROYA PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>120801</t>
+          <t>120802</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -575,32 +575,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LA OROYA</t>
+          <t>CHACAPALPA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.5192616</t>
+          <t>-11.7294441</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-75.9016488</t>
+          <t>-75.75581143</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CENTRO DE ASISTENCIA MADICA Y MEDICINA OCUPACIONAL CLANICA GONZALES SEDE LA OROYA</t>
+          <t>CHACAPALPA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AVENIDA AV. AREVALO 1031 - URB. TACARPANA - SANTA ROSA DE SACCO DISTRITO SANTA ROSA DE SACCO PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
+          <t>CALLE CALLE TARMA S/N NUMERO S/N DISTRITO CHACAPALPA PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,12 +617,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>120801</t>
+          <t>120810</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,37 +637,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LA OROYA</t>
+          <t>YAULI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-11.602088</t>
+          <t>-11.66810856</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-75.968907</t>
+          <t>-76.08748941</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO LA OROYA</t>
+          <t>YAULI - LA OROYA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CARRETERA CENTRAL DISTRITO LA OROYA PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
+          <t>JR. GRAU Nº 325 JR. GRAU Nº 325 YAULI YAULI JUNIN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">

--- a/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
+++ b/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>120801</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>YAULI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA_OROYA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>560</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>120801</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YAULI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA OROYA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-11.58001621</t>
@@ -544,55 +539,50 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>120801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>120801</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>YAULI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA_OROYA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>429</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>120802</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>YAULI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-11.7294441</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-75.75581143</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>CHACAPALPA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-11.7294441</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-75.75581143</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CHACAPALPA</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>CALLE CALLE TARMA S/N NUMERO S/N DISTRITO CHACAPALPA PROVINCIA YAULI DEPARTAMENTO JUNIN</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>120801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>120801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YAULI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LA_OROYA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>120810</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>YAULI</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>YAULI</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-11.66810856</t>
@@ -668,11 +653,6 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>120801</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
+++ b/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
+++ b/EstablecimientoSalud/excels/JUNIN-YAULI-LA_OROYA.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_OROYA</t>
+          <t>LA OROYA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
